--- a/03_Outputs/Agroindustrial_Occidente/07_Ambiental/ambiental.xlsx
+++ b/03_Outputs/Agroindustrial_Occidente/07_Ambiental/ambiental.xlsx
@@ -61,7 +61,7 @@
     <numFmt numFmtId="195" formatCode="0.0%"/>
     <numFmt numFmtId="196" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,23 +71,213 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -107,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -116,34 +306,68 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="172" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="175" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="177" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="192" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="16" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="18" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="14" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="15" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="16" fontId="22" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -472,14 +696,14 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1262,22 +1486,22 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>Antioquia</t>
         </is>
@@ -1493,17 +1717,17 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="61" t="inlineStr">
         <is>
           <t>perdida_ca</t>
         </is>
@@ -1581,17 +1805,17 @@
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="63" t="inlineStr">
         <is>
           <t>tipo</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="63" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
@@ -1769,17 +1993,17 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="65" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1845,22 +2069,23 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="67" t="inlineStr">
         <is>
           <t>imrc_deficit</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="67" t="inlineStr">
         <is>
           <t>imrc_exceso</t>
         </is>
@@ -1956,22 +2181,22 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="69" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="69" t="inlineStr">
         <is>
           <t>Pérdida de cobertura arbórea 2001-2023 (%)</t>
         </is>
@@ -2067,71 +2292,71 @@
   <dimension ref="A1:K127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="55.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>IRCA</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Nivel de riesgo</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>IRCA urbano</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Nivel riesgo urbano</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>IRCA rural</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Nivel riesgo rural</t>
         </is>
@@ -2159,7 +2384,7 @@
       <c r="E2">
         <v>2007</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="11">
         <v>15.2</v>
       </c>
       <c r="G2" t="inlineStr">
@@ -2167,7 +2392,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="13">
         <v>15.2</v>
       </c>
       <c r="I2" t="inlineStr">
@@ -2175,7 +2400,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J2" s="12" t="inlineStr">
+      <c r="J2" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2208,7 +2433,7 @@
       <c r="E3">
         <v>2007</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="11">
         <v>11.2</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -2216,7 +2441,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="13">
         <v>11.2</v>
       </c>
       <c r="I3" t="inlineStr">
@@ -2224,7 +2449,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J3" s="12" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2257,7 +2482,7 @@
       <c r="E4">
         <v>2007</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="11">
         <v>66.1</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -2265,7 +2490,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="13">
         <v>66.1</v>
       </c>
       <c r="I4" t="inlineStr">
@@ -2273,7 +2498,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2306,7 +2531,7 @@
       <c r="E5">
         <v>2007</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="11">
         <v>5.3</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -2314,7 +2539,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="13">
         <v>5.3</v>
       </c>
       <c r="I5" t="inlineStr">
@@ -2322,7 +2547,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2355,7 +2580,7 @@
       <c r="E6">
         <v>2007</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="11">
         <v>26.7</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -2363,7 +2588,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="13">
         <v>26.7</v>
       </c>
       <c r="I6" t="inlineStr">
@@ -2371,7 +2596,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2404,7 +2629,7 @@
       <c r="E7">
         <v>2007</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="11">
         <v>39.3</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -2412,7 +2637,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="13">
         <v>39.3</v>
       </c>
       <c r="I7" t="inlineStr">
@@ -2420,7 +2645,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2432,49 +2657,49 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="3">
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="10">
         <v>2007</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="12">
         <v>27.3</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H8" s="11">
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H8" s="14">
         <v>27.3</v>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J8" s="13" t="e">
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2502,7 +2727,7 @@
       <c r="E9">
         <v>2008</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="11">
         <v>5.1</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -2510,7 +2735,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="13">
         <v>5.1</v>
       </c>
       <c r="I9" t="inlineStr">
@@ -2518,7 +2743,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2551,7 +2776,7 @@
       <c r="E10">
         <v>2008</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="11">
         <v>2.5</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -2559,7 +2784,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="13">
         <v>2.5</v>
       </c>
       <c r="I10" t="inlineStr">
@@ -2567,7 +2792,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2600,7 +2825,7 @@
       <c r="E11">
         <v>2008</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="11">
         <v>76.7</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -2608,7 +2833,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="13">
         <v>74.5</v>
       </c>
       <c r="I11" t="inlineStr">
@@ -2616,7 +2841,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="15">
         <v>84.5</v>
       </c>
       <c r="K11" t="inlineStr">
@@ -2647,7 +2872,7 @@
       <c r="E12">
         <v>2008</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="11">
         <v>4.1</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -2655,7 +2880,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="13">
         <v>4.1</v>
       </c>
       <c r="I12" t="inlineStr">
@@ -2663,7 +2888,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2696,7 +2921,7 @@
       <c r="E13">
         <v>2008</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="11">
         <v>19.9</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -2704,7 +2929,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="13">
         <v>19.9</v>
       </c>
       <c r="I13" t="inlineStr">
@@ -2712,7 +2937,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="J13" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2745,7 +2970,7 @@
       <c r="E14">
         <v>2008</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="11">
         <v>37.6</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -2753,7 +2978,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="13">
         <v>37.6</v>
       </c>
       <c r="I14" t="inlineStr">
@@ -2761,7 +2986,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2773,49 +2998,49 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="3">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="10">
         <v>2008</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="12">
         <v>24.3166666666667</v>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H15" s="11">
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H15" s="14">
         <v>23.95</v>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J15" s="13">
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" s="16">
         <v>84.5</v>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2843,7 +3068,7 @@
       <c r="E16">
         <v>2009</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="11">
         <v>1.5</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -2851,7 +3076,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="13">
         <v>1.5</v>
       </c>
       <c r="I16" t="inlineStr">
@@ -2859,7 +3084,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2892,7 +3117,7 @@
       <c r="E17">
         <v>2009</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="11">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -2900,7 +3125,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="13">
         <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
@@ -2908,7 +3133,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="J17" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2941,7 +3166,7 @@
       <c r="E18">
         <v>2009</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="11">
         <v>11.2</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -2949,7 +3174,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="13">
         <v>11.2</v>
       </c>
       <c r="I18" t="inlineStr">
@@ -2957,7 +3182,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J18" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2990,7 +3215,7 @@
       <c r="E19">
         <v>2009</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="11">
         <v>2.9</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -2998,7 +3223,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="13">
         <v>2.9</v>
       </c>
       <c r="I19" t="inlineStr">
@@ -3006,7 +3231,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="J19" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3039,7 +3264,7 @@
       <c r="E20">
         <v>2009</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="11">
         <v>6.7</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -3047,7 +3272,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="13">
         <v>6.7</v>
       </c>
       <c r="I20" t="inlineStr">
@@ -3055,7 +3280,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J20" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3088,7 +3313,7 @@
       <c r="E21">
         <v>2009</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="11">
         <v>41.8</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -3096,7 +3321,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="13">
         <v>41.8</v>
       </c>
       <c r="I21" t="inlineStr">
@@ -3104,7 +3329,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J21" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3116,49 +3341,49 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E22" s="3">
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E22" s="10">
         <v>2009</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="12">
         <v>10.6833333333333</v>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H22" s="11">
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H22" s="14">
         <v>10.6833333333333</v>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J22" s="13" t="e">
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3186,7 +3411,7 @@
       <c r="E23">
         <v>2010</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="11">
         <v>16.5</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -3194,7 +3419,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="13">
         <v>1.4</v>
       </c>
       <c r="I23" t="inlineStr">
@@ -3202,7 +3427,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J23" s="12">
+      <c r="J23" s="15">
         <v>47.7</v>
       </c>
       <c r="K23" t="inlineStr">
@@ -3233,7 +3458,7 @@
       <c r="E24">
         <v>2010</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="11">
         <v>64.4</v>
       </c>
       <c r="G24" t="inlineStr">
@@ -3241,7 +3466,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="13">
         <v>58.2</v>
       </c>
       <c r="I24" t="inlineStr">
@@ -3249,7 +3474,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="J24" s="12">
+      <c r="J24" s="15">
         <v>97.3</v>
       </c>
       <c r="K24" t="inlineStr">
@@ -3280,7 +3505,7 @@
       <c r="E25">
         <v>2010</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="11">
         <v>31.9</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -3288,7 +3513,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="13">
         <v>8.6</v>
       </c>
       <c r="I25" t="inlineStr">
@@ -3296,7 +3521,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J25" s="12">
+      <c r="J25" s="15">
         <v>93.3</v>
       </c>
       <c r="K25" t="inlineStr">
@@ -3327,7 +3552,7 @@
       <c r="E26">
         <v>2010</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="11">
         <v>55.4</v>
       </c>
       <c r="G26" t="inlineStr">
@@ -3335,7 +3560,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="13">
         <v>8.2</v>
       </c>
       <c r="I26" t="inlineStr">
@@ -3343,7 +3568,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J26" s="12">
+      <c r="J26" s="15">
         <v>97.3</v>
       </c>
       <c r="K26" t="inlineStr">
@@ -3374,7 +3599,7 @@
       <c r="E27">
         <v>2010</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="11">
         <v>61.4</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -3382,7 +3607,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="13">
         <v>19.6</v>
       </c>
       <c r="I27" t="inlineStr">
@@ -3390,7 +3615,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J27" s="12">
+      <c r="J27" s="15">
         <v>97.3</v>
       </c>
       <c r="K27" t="inlineStr">
@@ -3421,7 +3646,7 @@
       <c r="E28">
         <v>2010</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="11">
         <v>40.6</v>
       </c>
       <c r="G28" t="inlineStr">
@@ -3429,7 +3654,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="13">
         <v>24.8</v>
       </c>
       <c r="I28" t="inlineStr">
@@ -3437,7 +3662,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="15">
         <v>97.3</v>
       </c>
       <c r="K28" t="inlineStr">
@@ -3447,49 +3672,49 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E29" s="3">
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E29" s="10">
         <v>2010</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="12">
         <v>45.0333333333333</v>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H29" s="11">
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H29" s="14">
         <v>20.1333333333333</v>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J29" s="13">
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J29" s="16">
         <v>88.3666666666667</v>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3517,7 +3742,7 @@
       <c r="E30">
         <v>2011</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="11">
         <v>19.4</v>
       </c>
       <c r="G30" t="inlineStr">
@@ -3525,7 +3750,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="13">
         <v>2.9</v>
       </c>
       <c r="I30" t="inlineStr">
@@ -3533,7 +3758,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="15">
         <v>36.5</v>
       </c>
       <c r="K30" t="inlineStr">
@@ -3564,7 +3789,7 @@
       <c r="E31">
         <v>2011</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="11">
         <v>76.5</v>
       </c>
       <c r="G31" t="inlineStr">
@@ -3572,7 +3797,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="13">
         <v>71.4</v>
       </c>
       <c r="I31" t="inlineStr">
@@ -3580,7 +3805,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="J31" s="12">
+      <c r="J31" s="15">
         <v>97.3</v>
       </c>
       <c r="K31" t="inlineStr">
@@ -3611,7 +3836,7 @@
       <c r="E32">
         <v>2011</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="11">
         <v>26.4</v>
       </c>
       <c r="G32" t="inlineStr">
@@ -3619,7 +3844,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="13">
         <v>3.8</v>
       </c>
       <c r="I32" t="inlineStr">
@@ -3627,7 +3852,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J32" s="12">
+      <c r="J32" s="15">
         <v>97.3</v>
       </c>
       <c r="K32" t="inlineStr">
@@ -3658,7 +3883,7 @@
       <c r="E33">
         <v>2011</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="11">
         <v>72.7</v>
       </c>
       <c r="G33" t="inlineStr">
@@ -3666,7 +3891,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="13">
         <v>0.7</v>
       </c>
       <c r="I33" t="inlineStr">
@@ -3674,7 +3899,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="15">
         <v>97.3</v>
       </c>
       <c r="K33" t="inlineStr">
@@ -3705,7 +3930,7 @@
       <c r="E34">
         <v>2011</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="11">
         <v>70.5</v>
       </c>
       <c r="G34" t="inlineStr">
@@ -3713,7 +3938,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="13">
         <v>27.4</v>
       </c>
       <c r="I34" t="inlineStr">
@@ -3721,7 +3946,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J34" s="12">
+      <c r="J34" s="15">
         <v>97.3</v>
       </c>
       <c r="K34" t="inlineStr">
@@ -3752,7 +3977,7 @@
       <c r="E35">
         <v>2011</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="11">
         <v>50.2</v>
       </c>
       <c r="G35" t="inlineStr">
@@ -3760,7 +3985,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="13">
         <v>15.1</v>
       </c>
       <c r="I35" t="inlineStr">
@@ -3768,7 +3993,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J35" s="12">
+      <c r="J35" s="15">
         <v>97.3</v>
       </c>
       <c r="K35" t="inlineStr">
@@ -3778,49 +4003,49 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E36" s="3">
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E36" s="10">
         <v>2011</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="12">
         <v>52.6166666666667</v>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H36" s="11">
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H36" s="14">
         <v>20.2166666666667</v>
       </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J36" s="13">
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J36" s="16">
         <v>87.1666666666667</v>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3848,7 +4073,7 @@
       <c r="E37">
         <v>2012</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="11">
         <v>7.2</v>
       </c>
       <c r="G37" t="inlineStr">
@@ -3856,7 +4081,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="13">
         <v>7.2</v>
       </c>
       <c r="I37" t="inlineStr">
@@ -3864,7 +4089,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J37" s="12" t="inlineStr">
+      <c r="J37" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3897,7 +4122,7 @@
       <c r="E38">
         <v>2012</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="11">
         <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
@@ -3905,7 +4130,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="13">
         <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
@@ -3913,7 +4138,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J38" s="12" t="inlineStr">
+      <c r="J38" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3946,7 +4171,7 @@
       <c r="E39">
         <v>2012</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="11">
         <v>20.6</v>
       </c>
       <c r="G39" t="inlineStr">
@@ -3954,7 +4179,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H39" s="10">
+      <c r="H39" s="13">
         <v>20.6</v>
       </c>
       <c r="I39" t="inlineStr">
@@ -3962,7 +4187,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J39" s="12" t="inlineStr">
+      <c r="J39" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3995,7 +4220,7 @@
       <c r="E40">
         <v>2012</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="11">
         <v>2.3</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -4003,7 +4228,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="13">
         <v>2.3</v>
       </c>
       <c r="I40" t="inlineStr">
@@ -4011,7 +4236,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J40" s="12" t="inlineStr">
+      <c r="J40" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4044,7 +4269,7 @@
       <c r="E41">
         <v>2012</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="11">
         <v>25</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -4052,7 +4277,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H41" s="10">
+      <c r="H41" s="13">
         <v>25</v>
       </c>
       <c r="I41" t="inlineStr">
@@ -4060,7 +4285,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J41" s="12" t="inlineStr">
+      <c r="J41" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4093,7 +4318,7 @@
       <c r="E42">
         <v>2012</v>
       </c>
-      <c r="F42" s="8">
+      <c r="F42" s="11">
         <v>7.8</v>
       </c>
       <c r="G42" t="inlineStr">
@@ -4101,7 +4326,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="13">
         <v>7.8</v>
       </c>
       <c r="I42" t="inlineStr">
@@ -4109,7 +4334,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J42" s="12" t="inlineStr">
+      <c r="J42" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4121,49 +4346,49 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E43" s="3">
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E43" s="10">
         <v>2012</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="12">
         <v>10.4833333333333</v>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H43" s="11">
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H43" s="14">
         <v>10.4833333333333</v>
       </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J43" s="13" t="e">
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J43" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K43" s="3" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4191,7 +4416,7 @@
       <c r="E44">
         <v>2013</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="11">
         <v>5.8</v>
       </c>
       <c r="G44" t="inlineStr">
@@ -4199,7 +4424,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="13">
         <v>5.8</v>
       </c>
       <c r="I44" t="inlineStr">
@@ -4207,7 +4432,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="J44" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4240,7 +4465,7 @@
       <c r="E45">
         <v>2013</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="11">
         <v>0.9</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -4248,7 +4473,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="13">
         <v>0.9</v>
       </c>
       <c r="I45" t="inlineStr">
@@ -4256,7 +4481,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J45" s="12" t="inlineStr">
+      <c r="J45" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4289,7 +4514,7 @@
       <c r="E46">
         <v>2013</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="11">
         <v>3.7</v>
       </c>
       <c r="G46" t="inlineStr">
@@ -4297,7 +4522,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="13">
         <v>3.7</v>
       </c>
       <c r="I46" t="inlineStr">
@@ -4305,7 +4530,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J46" s="12" t="inlineStr">
+      <c r="J46" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4338,7 +4563,7 @@
       <c r="E47">
         <v>2013</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="11">
         <v>0.5</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -4346,7 +4571,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="13">
         <v>0.5</v>
       </c>
       <c r="I47" t="inlineStr">
@@ -4354,7 +4579,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J47" s="12" t="inlineStr">
+      <c r="J47" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4387,7 +4612,7 @@
       <c r="E48">
         <v>2013</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="11">
         <v>13.1</v>
       </c>
       <c r="G48" t="inlineStr">
@@ -4395,7 +4620,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="13">
         <v>13.1</v>
       </c>
       <c r="I48" t="inlineStr">
@@ -4403,7 +4628,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J48" s="12" t="inlineStr">
+      <c r="J48" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4436,7 +4661,7 @@
       <c r="E49">
         <v>2013</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="11">
         <v>6.1</v>
       </c>
       <c r="G49" t="inlineStr">
@@ -4444,7 +4669,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H49" s="10">
+      <c r="H49" s="13">
         <v>6.1</v>
       </c>
       <c r="I49" t="inlineStr">
@@ -4452,7 +4677,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J49" s="12" t="inlineStr">
+      <c r="J49" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4464,49 +4689,49 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E50" s="3">
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E50" s="10">
         <v>2013</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F50" s="12">
         <v>5.01666666666667</v>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H50" s="11">
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H50" s="14">
         <v>5.01666666666667</v>
       </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J50" s="13" t="e">
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J50" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="K50" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4534,7 +4759,7 @@
       <c r="E51">
         <v>2014</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="11">
         <v>6.1</v>
       </c>
       <c r="G51" t="inlineStr">
@@ -4542,7 +4767,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="13">
         <v>6.1</v>
       </c>
       <c r="I51" t="inlineStr">
@@ -4550,7 +4775,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J51" s="12" t="inlineStr">
+      <c r="J51" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4583,7 +4808,7 @@
       <c r="E52">
         <v>2014</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="11">
         <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
@@ -4591,7 +4816,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="13">
         <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
@@ -4599,7 +4824,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J52" s="12" t="inlineStr">
+      <c r="J52" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4632,7 +4857,7 @@
       <c r="E53">
         <v>2014</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="11">
         <v>3.7</v>
       </c>
       <c r="G53" t="inlineStr">
@@ -4640,7 +4865,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H53" s="10">
+      <c r="H53" s="13">
         <v>3.7</v>
       </c>
       <c r="I53" t="inlineStr">
@@ -4648,7 +4873,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J53" s="12" t="inlineStr">
+      <c r="J53" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4681,7 +4906,7 @@
       <c r="E54">
         <v>2014</v>
       </c>
-      <c r="F54" s="8">
+      <c r="F54" s="11">
         <v>0.6</v>
       </c>
       <c r="G54" t="inlineStr">
@@ -4689,7 +4914,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H54" s="10">
+      <c r="H54" s="13">
         <v>0.6</v>
       </c>
       <c r="I54" t="inlineStr">
@@ -4697,7 +4922,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J54" s="12" t="inlineStr">
+      <c r="J54" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4730,7 +4955,7 @@
       <c r="E55">
         <v>2014</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="11">
         <v>6.7</v>
       </c>
       <c r="G55" t="inlineStr">
@@ -4738,7 +4963,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H55" s="10">
+      <c r="H55" s="13">
         <v>6.7</v>
       </c>
       <c r="I55" t="inlineStr">
@@ -4746,7 +4971,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J55" s="12" t="inlineStr">
+      <c r="J55" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4779,7 +5004,7 @@
       <c r="E56">
         <v>2014</v>
       </c>
-      <c r="F56" s="8">
+      <c r="F56" s="11">
         <v>7.6</v>
       </c>
       <c r="G56" t="inlineStr">
@@ -4787,7 +5012,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H56" s="10">
+      <c r="H56" s="13">
         <v>8.1</v>
       </c>
       <c r="I56" t="inlineStr">
@@ -4795,7 +5020,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J56" s="12" t="inlineStr">
+      <c r="J56" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4807,49 +5032,49 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E57" s="3">
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E57" s="10">
         <v>2014</v>
       </c>
-      <c r="F57" s="9">
+      <c r="F57" s="12">
         <v>4.11666666666667</v>
       </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H57" s="11">
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H57" s="14">
         <v>4.2</v>
       </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J57" s="13" t="e">
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J57" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K57" s="3" t="inlineStr">
+      <c r="K57" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4877,7 +5102,7 @@
       <c r="E58">
         <v>2015</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="11">
         <v>4.6</v>
       </c>
       <c r="G58" t="inlineStr">
@@ -4885,7 +5110,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H58" s="10">
+      <c r="H58" s="13">
         <v>4.6</v>
       </c>
       <c r="I58" t="inlineStr">
@@ -4893,7 +5118,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J58" s="12" t="inlineStr">
+      <c r="J58" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4926,7 +5151,7 @@
       <c r="E59">
         <v>2015</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="11">
         <v>2.8</v>
       </c>
       <c r="G59" t="inlineStr">
@@ -4934,7 +5159,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H59" s="10">
+      <c r="H59" s="13">
         <v>2.3</v>
       </c>
       <c r="I59" t="inlineStr">
@@ -4942,7 +5167,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J59" s="12" t="inlineStr">
+      <c r="J59" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4975,7 +5200,7 @@
       <c r="E60">
         <v>2015</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="11">
         <v>2.4</v>
       </c>
       <c r="G60" t="inlineStr">
@@ -4983,7 +5208,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H60" s="10">
+      <c r="H60" s="13">
         <v>2.4</v>
       </c>
       <c r="I60" t="inlineStr">
@@ -4991,7 +5216,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J60" s="12" t="inlineStr">
+      <c r="J60" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5024,7 +5249,7 @@
       <c r="E61">
         <v>2015</v>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="11">
         <v>1.8</v>
       </c>
       <c r="G61" t="inlineStr">
@@ -5032,7 +5257,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H61" s="10">
+      <c r="H61" s="13">
         <v>1.8</v>
       </c>
       <c r="I61" t="inlineStr">
@@ -5040,7 +5265,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J61" s="12" t="inlineStr">
+      <c r="J61" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5073,7 +5298,7 @@
       <c r="E62">
         <v>2015</v>
       </c>
-      <c r="F62" s="8">
+      <c r="F62" s="11">
         <v>15.4</v>
       </c>
       <c r="G62" t="inlineStr">
@@ -5081,7 +5306,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H62" s="10">
+      <c r="H62" s="13">
         <v>15.4</v>
       </c>
       <c r="I62" t="inlineStr">
@@ -5089,7 +5314,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J62" s="12" t="inlineStr">
+      <c r="J62" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5122,7 +5347,7 @@
       <c r="E63">
         <v>2015</v>
       </c>
-      <c r="F63" s="8">
+      <c r="F63" s="11">
         <v>9.6</v>
       </c>
       <c r="G63" t="inlineStr">
@@ -5130,7 +5355,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H63" s="10">
+      <c r="H63" s="13">
         <v>9.7</v>
       </c>
       <c r="I63" t="inlineStr">
@@ -5138,7 +5363,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J63" s="12" t="inlineStr">
+      <c r="J63" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5150,49 +5375,49 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E64" s="3">
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E64" s="10">
         <v>2015</v>
       </c>
-      <c r="F64" s="9">
+      <c r="F64" s="12">
         <v>6.1</v>
       </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H64" s="11">
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H64" s="14">
         <v>6.03333333333333</v>
       </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J64" s="13" t="e">
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J64" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K64" s="3" t="inlineStr">
+      <c r="K64" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5220,7 +5445,7 @@
       <c r="E65">
         <v>2016</v>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="11">
         <v>10.6</v>
       </c>
       <c r="G65" t="inlineStr">
@@ -5228,7 +5453,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H65" s="10">
+      <c r="H65" s="13">
         <v>10.6</v>
       </c>
       <c r="I65" t="inlineStr">
@@ -5236,7 +5461,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J65" s="12" t="inlineStr">
+      <c r="J65" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5269,7 +5494,7 @@
       <c r="E66">
         <v>2016</v>
       </c>
-      <c r="F66" s="8">
+      <c r="F66" s="11">
         <v>0</v>
       </c>
       <c r="G66" t="inlineStr">
@@ -5277,7 +5502,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H66" s="10">
+      <c r="H66" s="13">
         <v>0</v>
       </c>
       <c r="I66" t="inlineStr">
@@ -5285,7 +5510,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J66" s="12" t="inlineStr">
+      <c r="J66" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5318,7 +5543,7 @@
       <c r="E67">
         <v>2016</v>
       </c>
-      <c r="F67" s="8">
+      <c r="F67" s="11">
         <v>13</v>
       </c>
       <c r="G67" t="inlineStr">
@@ -5326,7 +5551,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H67" s="10">
+      <c r="H67" s="13">
         <v>0.9</v>
       </c>
       <c r="I67" t="inlineStr">
@@ -5334,7 +5559,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J67" s="12" t="inlineStr">
+      <c r="J67" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5367,7 +5592,7 @@
       <c r="E68">
         <v>2016</v>
       </c>
-      <c r="F68" s="8">
+      <c r="F68" s="11">
         <v>0</v>
       </c>
       <c r="G68" t="inlineStr">
@@ -5375,7 +5600,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H68" s="10">
+      <c r="H68" s="13">
         <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
@@ -5383,7 +5608,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J68" s="12" t="inlineStr">
+      <c r="J68" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5416,7 +5641,7 @@
       <c r="E69">
         <v>2016</v>
       </c>
-      <c r="F69" s="8">
+      <c r="F69" s="11">
         <v>0</v>
       </c>
       <c r="G69" t="inlineStr">
@@ -5424,7 +5649,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H69" s="10">
+      <c r="H69" s="13">
         <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
@@ -5432,7 +5657,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J69" s="12" t="inlineStr">
+      <c r="J69" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5465,7 +5690,7 @@
       <c r="E70">
         <v>2016</v>
       </c>
-      <c r="F70" s="8">
+      <c r="F70" s="11">
         <v>5.3</v>
       </c>
       <c r="G70" t="inlineStr">
@@ -5473,7 +5698,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H70" s="10">
+      <c r="H70" s="13">
         <v>6.4</v>
       </c>
       <c r="I70" t="inlineStr">
@@ -5481,7 +5706,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J70" s="12" t="inlineStr">
+      <c r="J70" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5493,49 +5718,49 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E71" s="3">
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E71" s="10">
         <v>2016</v>
       </c>
-      <c r="F71" s="9">
+      <c r="F71" s="12">
         <v>4.81666666666667</v>
       </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H71" s="11">
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H71" s="14">
         <v>2.98333333333333</v>
       </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J71" s="13" t="e">
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J71" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K71" s="3" t="inlineStr">
+      <c r="K71" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5563,7 +5788,7 @@
       <c r="E72">
         <v>2017</v>
       </c>
-      <c r="F72" s="8">
+      <c r="F72" s="11">
         <v>1.3</v>
       </c>
       <c r="G72" t="inlineStr">
@@ -5571,7 +5796,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H72" s="10">
+      <c r="H72" s="13">
         <v>1.3</v>
       </c>
       <c r="I72" t="inlineStr">
@@ -5579,7 +5804,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J72" s="12" t="inlineStr">
+      <c r="J72" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5612,7 +5837,7 @@
       <c r="E73">
         <v>2017</v>
       </c>
-      <c r="F73" s="8">
+      <c r="F73" s="11">
         <v>2.8</v>
       </c>
       <c r="G73" t="inlineStr">
@@ -5620,7 +5845,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H73" s="10">
+      <c r="H73" s="13">
         <v>3.9</v>
       </c>
       <c r="I73" t="inlineStr">
@@ -5628,7 +5853,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J73" s="12" t="inlineStr">
+      <c r="J73" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5661,7 +5886,7 @@
       <c r="E74">
         <v>2017</v>
       </c>
-      <c r="F74" s="8">
+      <c r="F74" s="11">
         <v>18.3</v>
       </c>
       <c r="G74" t="inlineStr">
@@ -5669,7 +5894,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H74" s="10">
+      <c r="H74" s="13">
         <v>1.3</v>
       </c>
       <c r="I74" t="inlineStr">
@@ -5677,7 +5902,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J74" s="12" t="inlineStr">
+      <c r="J74" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5710,7 +5935,7 @@
       <c r="E75">
         <v>2017</v>
       </c>
-      <c r="F75" s="8">
+      <c r="F75" s="11">
         <v>0.4</v>
       </c>
       <c r="G75" t="inlineStr">
@@ -5718,7 +5943,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H75" s="10">
+      <c r="H75" s="13">
         <v>0.4</v>
       </c>
       <c r="I75" t="inlineStr">
@@ -5726,7 +5951,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J75" s="12" t="inlineStr">
+      <c r="J75" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5759,7 +5984,7 @@
       <c r="E76">
         <v>2017</v>
       </c>
-      <c r="F76" s="8">
+      <c r="F76" s="11">
         <v>7.7</v>
       </c>
       <c r="G76" t="inlineStr">
@@ -5767,7 +5992,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H76" s="10">
+      <c r="H76" s="13">
         <v>7.7</v>
       </c>
       <c r="I76" t="inlineStr">
@@ -5775,7 +6000,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J76" s="12" t="inlineStr">
+      <c r="J76" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5808,7 +6033,7 @@
       <c r="E77">
         <v>2017</v>
       </c>
-      <c r="F77" s="8">
+      <c r="F77" s="11">
         <v>3.2</v>
       </c>
       <c r="G77" t="inlineStr">
@@ -5816,7 +6041,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H77" s="10">
+      <c r="H77" s="13">
         <v>2.8</v>
       </c>
       <c r="I77" t="inlineStr">
@@ -5824,7 +6049,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J77" s="12" t="inlineStr">
+      <c r="J77" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5836,49 +6061,49 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E78" s="3">
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E78" s="10">
         <v>2017</v>
       </c>
-      <c r="F78" s="9">
+      <c r="F78" s="12">
         <v>5.61666666666667</v>
       </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H78" s="11">
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H78" s="14">
         <v>2.9</v>
       </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J78" s="13" t="e">
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J78" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K78" s="3" t="inlineStr">
+      <c r="K78" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5906,7 +6131,7 @@
       <c r="E79">
         <v>2018</v>
       </c>
-      <c r="F79" s="8">
+      <c r="F79" s="11">
         <v>4.4</v>
       </c>
       <c r="G79" t="inlineStr">
@@ -5914,7 +6139,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H79" s="10">
+      <c r="H79" s="13">
         <v>4.4</v>
       </c>
       <c r="I79" t="inlineStr">
@@ -5922,7 +6147,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J79" s="12" t="inlineStr">
+      <c r="J79" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5955,7 +6180,7 @@
       <c r="E80">
         <v>2018</v>
       </c>
-      <c r="F80" s="8">
+      <c r="F80" s="11">
         <v>0.5</v>
       </c>
       <c r="G80" t="inlineStr">
@@ -5963,7 +6188,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H80" s="10">
+      <c r="H80" s="13">
         <v>0.5</v>
       </c>
       <c r="I80" t="inlineStr">
@@ -5971,7 +6196,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J80" s="12" t="inlineStr">
+      <c r="J80" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6004,7 +6229,7 @@
       <c r="E81">
         <v>2018</v>
       </c>
-      <c r="F81" s="8">
+      <c r="F81" s="11">
         <v>11.9</v>
       </c>
       <c r="G81" t="inlineStr">
@@ -6012,7 +6237,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H81" s="10">
+      <c r="H81" s="13">
         <v>11.9</v>
       </c>
       <c r="I81" t="inlineStr">
@@ -6020,7 +6245,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J81" s="12" t="inlineStr">
+      <c r="J81" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6053,7 +6278,7 @@
       <c r="E82">
         <v>2018</v>
       </c>
-      <c r="F82" s="8">
+      <c r="F82" s="11">
         <v>0</v>
       </c>
       <c r="G82" t="inlineStr">
@@ -6061,7 +6286,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H82" s="10">
+      <c r="H82" s="13">
         <v>0</v>
       </c>
       <c r="I82" t="inlineStr">
@@ -6069,7 +6294,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J82" s="12" t="inlineStr">
+      <c r="J82" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6102,7 +6327,7 @@
       <c r="E83">
         <v>2018</v>
       </c>
-      <c r="F83" s="8">
+      <c r="F83" s="11">
         <v>3.1</v>
       </c>
       <c r="G83" t="inlineStr">
@@ -6110,7 +6335,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H83" s="10">
+      <c r="H83" s="13">
         <v>3.1</v>
       </c>
       <c r="I83" t="inlineStr">
@@ -6118,7 +6343,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J83" s="12" t="inlineStr">
+      <c r="J83" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6151,7 +6376,7 @@
       <c r="E84">
         <v>2018</v>
       </c>
-      <c r="F84" s="8">
+      <c r="F84" s="11">
         <v>3.3</v>
       </c>
       <c r="G84" t="inlineStr">
@@ -6159,7 +6384,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H84" s="10">
+      <c r="H84" s="13">
         <v>3.3</v>
       </c>
       <c r="I84" t="inlineStr">
@@ -6167,7 +6392,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J84" s="12" t="inlineStr">
+      <c r="J84" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6179,49 +6404,49 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E85" s="3">
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E85" s="10">
         <v>2018</v>
       </c>
-      <c r="F85" s="9">
+      <c r="F85" s="12">
         <v>3.86666666666667</v>
       </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H85" s="11">
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H85" s="14">
         <v>3.86666666666667</v>
       </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J85" s="13" t="e">
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J85" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K85" s="3" t="inlineStr">
+      <c r="K85" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6249,7 +6474,7 @@
       <c r="E86">
         <v>2019</v>
       </c>
-      <c r="F86" s="8">
+      <c r="F86" s="11">
         <v>3.4</v>
       </c>
       <c r="G86" t="inlineStr">
@@ -6257,7 +6482,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H86" s="10">
+      <c r="H86" s="13">
         <v>3.4</v>
       </c>
       <c r="I86" t="inlineStr">
@@ -6265,7 +6490,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J86" s="12" t="inlineStr">
+      <c r="J86" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6298,7 +6523,7 @@
       <c r="E87">
         <v>2019</v>
       </c>
-      <c r="F87" s="8">
+      <c r="F87" s="11">
         <v>0</v>
       </c>
       <c r="G87" t="inlineStr">
@@ -6306,7 +6531,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H87" s="10">
+      <c r="H87" s="13">
         <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
@@ -6314,7 +6539,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J87" s="12" t="inlineStr">
+      <c r="J87" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6347,7 +6572,7 @@
       <c r="E88">
         <v>2019</v>
       </c>
-      <c r="F88" s="8">
+      <c r="F88" s="11">
         <v>12.3</v>
       </c>
       <c r="G88" t="inlineStr">
@@ -6355,7 +6580,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H88" s="10">
+      <c r="H88" s="13">
         <v>12.3</v>
       </c>
       <c r="I88" t="inlineStr">
@@ -6363,7 +6588,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J88" s="12" t="inlineStr">
+      <c r="J88" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6396,7 +6621,7 @@
       <c r="E89">
         <v>2019</v>
       </c>
-      <c r="F89" s="8">
+      <c r="F89" s="11">
         <v>0</v>
       </c>
       <c r="G89" t="inlineStr">
@@ -6404,7 +6629,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H89" s="10">
+      <c r="H89" s="13">
         <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
@@ -6412,7 +6637,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J89" s="12" t="inlineStr">
+      <c r="J89" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6445,7 +6670,7 @@
       <c r="E90">
         <v>2019</v>
       </c>
-      <c r="F90" s="8">
+      <c r="F90" s="11">
         <v>0.8</v>
       </c>
       <c r="G90" t="inlineStr">
@@ -6453,7 +6678,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H90" s="10">
+      <c r="H90" s="13">
         <v>0.8</v>
       </c>
       <c r="I90" t="inlineStr">
@@ -6461,7 +6686,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J90" s="12" t="inlineStr">
+      <c r="J90" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6494,7 +6719,7 @@
       <c r="E91">
         <v>2019</v>
       </c>
-      <c r="F91" s="8">
+      <c r="F91" s="11">
         <v>7.6</v>
       </c>
       <c r="G91" t="inlineStr">
@@ -6502,7 +6727,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H91" s="10">
+      <c r="H91" s="13">
         <v>7.6</v>
       </c>
       <c r="I91" t="inlineStr">
@@ -6510,7 +6735,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J91" s="12" t="inlineStr">
+      <c r="J91" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6522,49 +6747,49 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E92" s="3">
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E92" s="10">
         <v>2019</v>
       </c>
-      <c r="F92" s="9">
+      <c r="F92" s="12">
         <v>4.01666666666667</v>
       </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H92" s="11">
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H92" s="14">
         <v>4.01666666666667</v>
       </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J92" s="13" t="e">
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J92" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K92" s="3" t="inlineStr">
+      <c r="K92" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6592,7 +6817,7 @@
       <c r="E93">
         <v>2020</v>
       </c>
-      <c r="F93" s="8">
+      <c r="F93" s="11">
         <v>1.8</v>
       </c>
       <c r="G93" t="inlineStr">
@@ -6600,7 +6825,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H93" s="10">
+      <c r="H93" s="13">
         <v>1.8</v>
       </c>
       <c r="I93" t="inlineStr">
@@ -6608,7 +6833,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J93" s="12" t="inlineStr">
+      <c r="J93" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6641,7 +6866,7 @@
       <c r="E94">
         <v>2020</v>
       </c>
-      <c r="F94" s="8">
+      <c r="F94" s="11">
         <v>2.4</v>
       </c>
       <c r="G94" t="inlineStr">
@@ -6649,7 +6874,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H94" s="10">
+      <c r="H94" s="13">
         <v>2.4</v>
       </c>
       <c r="I94" t="inlineStr">
@@ -6657,7 +6882,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J94" s="12" t="inlineStr">
+      <c r="J94" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6690,7 +6915,7 @@
       <c r="E95">
         <v>2020</v>
       </c>
-      <c r="F95" s="8">
+      <c r="F95" s="11">
         <v>0.1</v>
       </c>
       <c r="G95" t="inlineStr">
@@ -6698,7 +6923,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H95" s="10">
+      <c r="H95" s="13">
         <v>0.1</v>
       </c>
       <c r="I95" t="inlineStr">
@@ -6706,7 +6931,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J95" s="12" t="inlineStr">
+      <c r="J95" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6739,7 +6964,7 @@
       <c r="E96">
         <v>2020</v>
       </c>
-      <c r="F96" s="8">
+      <c r="F96" s="11">
         <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
@@ -6747,7 +6972,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H96" s="10">
+      <c r="H96" s="13">
         <v>1</v>
       </c>
       <c r="I96" t="inlineStr">
@@ -6755,7 +6980,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J96" s="12" t="inlineStr">
+      <c r="J96" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6788,7 +7013,7 @@
       <c r="E97">
         <v>2020</v>
       </c>
-      <c r="F97" s="8">
+      <c r="F97" s="11">
         <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
@@ -6796,7 +7021,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H97" s="10">
+      <c r="H97" s="13">
         <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
@@ -6804,7 +7029,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J97" s="12" t="inlineStr">
+      <c r="J97" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6837,7 +7062,7 @@
       <c r="E98">
         <v>2020</v>
       </c>
-      <c r="F98" s="8">
+      <c r="F98" s="11">
         <v>9.3</v>
       </c>
       <c r="G98" t="inlineStr">
@@ -6845,7 +7070,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H98" s="10">
+      <c r="H98" s="13">
         <v>9.3</v>
       </c>
       <c r="I98" t="inlineStr">
@@ -6853,7 +7078,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J98" s="12" t="inlineStr">
+      <c r="J98" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6865,49 +7090,49 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E99" s="3">
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E99" s="10">
         <v>2020</v>
       </c>
-      <c r="F99" s="9">
+      <c r="F99" s="12">
         <v>2.43333333333333</v>
       </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H99" s="11">
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H99" s="14">
         <v>2.43333333333333</v>
       </c>
-      <c r="I99" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J99" s="13" t="e">
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J99" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K99" s="3" t="inlineStr">
+      <c r="K99" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6935,7 +7160,7 @@
       <c r="E100">
         <v>2021</v>
       </c>
-      <c r="F100" s="8">
+      <c r="F100" s="11">
         <v>3</v>
       </c>
       <c r="G100" t="inlineStr">
@@ -6943,7 +7168,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H100" s="10">
+      <c r="H100" s="13">
         <v>3</v>
       </c>
       <c r="I100" t="inlineStr">
@@ -6951,7 +7176,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J100" s="12" t="inlineStr">
+      <c r="J100" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6984,7 +7209,7 @@
       <c r="E101">
         <v>2021</v>
       </c>
-      <c r="F101" s="8">
+      <c r="F101" s="11">
         <v>1.3</v>
       </c>
       <c r="G101" t="inlineStr">
@@ -6992,7 +7217,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H101" s="10">
+      <c r="H101" s="13">
         <v>1.3</v>
       </c>
       <c r="I101" t="inlineStr">
@@ -7000,7 +7225,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J101" s="12" t="inlineStr">
+      <c r="J101" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7033,7 +7258,7 @@
       <c r="E102">
         <v>2021</v>
       </c>
-      <c r="F102" s="8">
+      <c r="F102" s="11">
         <v>0.9</v>
       </c>
       <c r="G102" t="inlineStr">
@@ -7041,7 +7266,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H102" s="10">
+      <c r="H102" s="13">
         <v>0.9</v>
       </c>
       <c r="I102" t="inlineStr">
@@ -7049,7 +7274,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J102" s="12" t="inlineStr">
+      <c r="J102" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7082,7 +7307,7 @@
       <c r="E103">
         <v>2021</v>
       </c>
-      <c r="F103" s="8">
+      <c r="F103" s="11">
         <v>2.2</v>
       </c>
       <c r="G103" t="inlineStr">
@@ -7090,7 +7315,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H103" s="10">
+      <c r="H103" s="13">
         <v>2.2</v>
       </c>
       <c r="I103" t="inlineStr">
@@ -7098,7 +7323,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J103" s="12" t="inlineStr">
+      <c r="J103" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7131,7 +7356,7 @@
       <c r="E104">
         <v>2021</v>
       </c>
-      <c r="F104" s="8">
+      <c r="F104" s="11">
         <v>1.2</v>
       </c>
       <c r="G104" t="inlineStr">
@@ -7139,7 +7364,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H104" s="10">
+      <c r="H104" s="13">
         <v>1.2</v>
       </c>
       <c r="I104" t="inlineStr">
@@ -7147,7 +7372,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J104" s="12" t="inlineStr">
+      <c r="J104" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7180,7 +7405,7 @@
       <c r="E105">
         <v>2021</v>
       </c>
-      <c r="F105" s="8">
+      <c r="F105" s="11">
         <v>9.2</v>
       </c>
       <c r="G105" t="inlineStr">
@@ -7188,7 +7413,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H105" s="10">
+      <c r="H105" s="13">
         <v>9.2</v>
       </c>
       <c r="I105" t="inlineStr">
@@ -7196,7 +7421,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J105" s="12" t="inlineStr">
+      <c r="J105" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7208,49 +7433,49 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E106" s="3">
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E106" s="10">
         <v>2021</v>
       </c>
-      <c r="F106" s="9">
+      <c r="F106" s="12">
         <v>2.96666666666667</v>
       </c>
-      <c r="G106" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H106" s="11">
+      <c r="G106" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H106" s="14">
         <v>2.96666666666667</v>
       </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J106" s="13" t="e">
+      <c r="I106" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J106" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K106" s="3" t="inlineStr">
+      <c r="K106" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7278,7 +7503,7 @@
       <c r="E107">
         <v>2022</v>
       </c>
-      <c r="F107" s="8">
+      <c r="F107" s="11">
         <v>6.5</v>
       </c>
       <c r="G107" t="inlineStr">
@@ -7286,7 +7511,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H107" s="10">
+      <c r="H107" s="13">
         <v>6.5</v>
       </c>
       <c r="I107" t="inlineStr">
@@ -7294,7 +7519,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J107" s="12" t="inlineStr">
+      <c r="J107" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7327,7 +7552,7 @@
       <c r="E108">
         <v>2022</v>
       </c>
-      <c r="F108" s="8">
+      <c r="F108" s="11">
         <v>0</v>
       </c>
       <c r="G108" t="inlineStr">
@@ -7335,7 +7560,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H108" s="10">
+      <c r="H108" s="13">
         <v>0</v>
       </c>
       <c r="I108" t="inlineStr">
@@ -7343,7 +7568,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J108" s="12" t="inlineStr">
+      <c r="J108" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7376,7 +7601,7 @@
       <c r="E109">
         <v>2022</v>
       </c>
-      <c r="F109" s="8">
+      <c r="F109" s="11">
         <v>0.9</v>
       </c>
       <c r="G109" t="inlineStr">
@@ -7384,7 +7609,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H109" s="10">
+      <c r="H109" s="13">
         <v>0.9</v>
       </c>
       <c r="I109" t="inlineStr">
@@ -7392,7 +7617,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J109" s="12" t="inlineStr">
+      <c r="J109" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7425,7 +7650,7 @@
       <c r="E110">
         <v>2022</v>
       </c>
-      <c r="F110" s="8">
+      <c r="F110" s="11">
         <v>0</v>
       </c>
       <c r="G110" t="inlineStr">
@@ -7433,7 +7658,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H110" s="10">
+      <c r="H110" s="13">
         <v>0</v>
       </c>
       <c r="I110" t="inlineStr">
@@ -7441,7 +7666,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J110" s="12" t="inlineStr">
+      <c r="J110" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7474,7 +7699,7 @@
       <c r="E111">
         <v>2022</v>
       </c>
-      <c r="F111" s="8">
+      <c r="F111" s="11">
         <v>2</v>
       </c>
       <c r="G111" t="inlineStr">
@@ -7482,7 +7707,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H111" s="10">
+      <c r="H111" s="13">
         <v>2</v>
       </c>
       <c r="I111" t="inlineStr">
@@ -7490,7 +7715,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J111" s="12" t="inlineStr">
+      <c r="J111" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7523,7 +7748,7 @@
       <c r="E112">
         <v>2022</v>
       </c>
-      <c r="F112" s="8">
+      <c r="F112" s="11">
         <v>4.9</v>
       </c>
       <c r="G112" t="inlineStr">
@@ -7531,7 +7756,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H112" s="10">
+      <c r="H112" s="13">
         <v>4.9</v>
       </c>
       <c r="I112" t="inlineStr">
@@ -7539,7 +7764,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J112" s="12" t="inlineStr">
+      <c r="J112" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7551,49 +7776,49 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E113" s="3">
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E113" s="10">
         <v>2022</v>
       </c>
-      <c r="F113" s="9">
+      <c r="F113" s="12">
         <v>2.38333333333333</v>
       </c>
-      <c r="G113" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H113" s="11">
+      <c r="G113" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H113" s="14">
         <v>2.38333333333333</v>
       </c>
-      <c r="I113" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J113" s="13" t="e">
+      <c r="I113" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J113" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K113" s="3" t="inlineStr">
+      <c r="K113" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7621,7 +7846,7 @@
       <c r="E114">
         <v>2023</v>
       </c>
-      <c r="F114" s="8">
+      <c r="F114" s="11">
         <v>10.2</v>
       </c>
       <c r="G114" t="inlineStr">
@@ -7629,7 +7854,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H114" s="10">
+      <c r="H114" s="13">
         <v>10.2</v>
       </c>
       <c r="I114" t="inlineStr">
@@ -7637,7 +7862,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J114" s="12" t="inlineStr">
+      <c r="J114" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7670,7 +7895,7 @@
       <c r="E115">
         <v>2023</v>
       </c>
-      <c r="F115" s="8">
+      <c r="F115" s="11">
         <v>0</v>
       </c>
       <c r="G115" t="inlineStr">
@@ -7678,7 +7903,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H115" s="10">
+      <c r="H115" s="13">
         <v>0</v>
       </c>
       <c r="I115" t="inlineStr">
@@ -7686,7 +7911,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J115" s="12" t="inlineStr">
+      <c r="J115" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7719,7 +7944,7 @@
       <c r="E116">
         <v>2023</v>
       </c>
-      <c r="F116" s="8">
+      <c r="F116" s="11">
         <v>0.4</v>
       </c>
       <c r="G116" t="inlineStr">
@@ -7727,7 +7952,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H116" s="10">
+      <c r="H116" s="13">
         <v>0.4</v>
       </c>
       <c r="I116" t="inlineStr">
@@ -7735,7 +7960,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J116" s="12" t="inlineStr">
+      <c r="J116" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7768,7 +7993,7 @@
       <c r="E117">
         <v>2023</v>
       </c>
-      <c r="F117" s="8">
+      <c r="F117" s="11">
         <v>2.8</v>
       </c>
       <c r="G117" t="inlineStr">
@@ -7776,7 +8001,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H117" s="10">
+      <c r="H117" s="13">
         <v>1.4</v>
       </c>
       <c r="I117" t="inlineStr">
@@ -7784,7 +8009,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J117" s="12">
+      <c r="J117" s="15">
         <v>100</v>
       </c>
       <c r="K117" t="inlineStr">
@@ -7815,7 +8040,7 @@
       <c r="E118">
         <v>2023</v>
       </c>
-      <c r="F118" s="8">
+      <c r="F118" s="11">
         <v>0</v>
       </c>
       <c r="G118" t="inlineStr">
@@ -7823,7 +8048,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H118" s="10">
+      <c r="H118" s="13">
         <v>0</v>
       </c>
       <c r="I118" t="inlineStr">
@@ -7831,7 +8056,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J118" s="12" t="inlineStr">
+      <c r="J118" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7864,7 +8089,7 @@
       <c r="E119">
         <v>2023</v>
       </c>
-      <c r="F119" s="8">
+      <c r="F119" s="11">
         <v>2.7</v>
       </c>
       <c r="G119" t="inlineStr">
@@ -7872,7 +8097,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H119" s="10">
+      <c r="H119" s="13">
         <v>2.7</v>
       </c>
       <c r="I119" t="inlineStr">
@@ -7880,7 +8105,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J119" s="12" t="inlineStr">
+      <c r="J119" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7892,49 +8117,49 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E120" s="3">
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E120" s="10">
         <v>2023</v>
       </c>
-      <c r="F120" s="9">
+      <c r="F120" s="12">
         <v>2.68333333333333</v>
       </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H120" s="11">
+      <c r="G120" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H120" s="14">
         <v>2.45</v>
       </c>
-      <c r="I120" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J120" s="13">
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J120" s="16">
         <v>100</v>
       </c>
-      <c r="K120" s="3" t="inlineStr">
+      <c r="K120" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7962,7 +8187,7 @@
       <c r="E121">
         <v>2024</v>
       </c>
-      <c r="F121" s="8">
+      <c r="F121" s="11">
         <v>7.2</v>
       </c>
       <c r="G121" t="inlineStr">
@@ -7970,7 +8195,7 @@
           <t>Bajo riesgo</t>
         </is>
       </c>
-      <c r="H121" s="10">
+      <c r="H121" s="13">
         <v>7.2</v>
       </c>
       <c r="I121" t="inlineStr">
@@ -7978,7 +8203,7 @@
           <t>Bajo riesgo</t>
         </is>
       </c>
-      <c r="J121" s="12" t="inlineStr">
+      <c r="J121" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8011,7 +8236,7 @@
       <c r="E122">
         <v>2024</v>
       </c>
-      <c r="F122" s="8">
+      <c r="F122" s="11">
         <v>2.9</v>
       </c>
       <c r="G122" t="inlineStr">
@@ -8019,7 +8244,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H122" s="10">
+      <c r="H122" s="13">
         <v>2.9</v>
       </c>
       <c r="I122" t="inlineStr">
@@ -8027,7 +8252,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J122" s="12" t="inlineStr">
+      <c r="J122" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8060,7 +8285,7 @@
       <c r="E123">
         <v>2024</v>
       </c>
-      <c r="F123" s="8">
+      <c r="F123" s="11">
         <v>1</v>
       </c>
       <c r="G123" t="inlineStr">
@@ -8068,7 +8293,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H123" s="10">
+      <c r="H123" s="13">
         <v>1</v>
       </c>
       <c r="I123" t="inlineStr">
@@ -8076,7 +8301,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J123" s="12" t="inlineStr">
+      <c r="J123" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8109,7 +8334,7 @@
       <c r="E124">
         <v>2024</v>
       </c>
-      <c r="F124" s="8">
+      <c r="F124" s="11">
         <v>1.8</v>
       </c>
       <c r="G124" t="inlineStr">
@@ -8117,7 +8342,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H124" s="10">
+      <c r="H124" s="13">
         <v>0.4</v>
       </c>
       <c r="I124" t="inlineStr">
@@ -8125,7 +8350,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J124" s="12">
+      <c r="J124" s="15">
         <v>32.5</v>
       </c>
       <c r="K124" t="inlineStr">
@@ -8156,7 +8381,7 @@
       <c r="E125">
         <v>2024</v>
       </c>
-      <c r="F125" s="8">
+      <c r="F125" s="11">
         <v>1.1</v>
       </c>
       <c r="G125" t="inlineStr">
@@ -8164,7 +8389,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H125" s="10">
+      <c r="H125" s="13">
         <v>1.1</v>
       </c>
       <c r="I125" t="inlineStr">
@@ -8172,7 +8397,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J125" s="12" t="inlineStr">
+      <c r="J125" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8205,7 +8430,7 @@
       <c r="E126">
         <v>2024</v>
       </c>
-      <c r="F126" s="8">
+      <c r="F126" s="11">
         <v>2.3</v>
       </c>
       <c r="G126" t="inlineStr">
@@ -8213,7 +8438,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H126" s="10">
+      <c r="H126" s="13">
         <v>2.3</v>
       </c>
       <c r="I126" t="inlineStr">
@@ -8221,7 +8446,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J126" s="12" t="inlineStr">
+      <c r="J126" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8233,49 +8458,49 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E127" s="3">
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E127" s="10">
         <v>2024</v>
       </c>
-      <c r="F127" s="9">
+      <c r="F127" s="12">
         <v>2.71666666666667</v>
       </c>
-      <c r="G127" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H127" s="11">
+      <c r="G127" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H127" s="14">
         <v>2.48333333333333</v>
       </c>
-      <c r="I127" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J127" s="13">
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J127" s="16">
         <v>32.5</v>
       </c>
-      <c r="K127" s="3" t="inlineStr">
+      <c r="K127" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8293,41 +8518,41 @@
   <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>Tipo de evento</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>Número de eventos</t>
         </is>
@@ -8357,7 +8582,7 @@
           <t>ACCIDENTE TRANSPORTE TERRESTRE</t>
         </is>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="20">
         <v>1</v>
       </c>
     </row>
@@ -8385,37 +8610,37 @@
           <t>ACCIDENTE TRANSPORTE TERRESTRE</t>
         </is>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="20">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>ACCIDENTE TRANSPORTE TERRESTRE</t>
         </is>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="21">
         <v>4</v>
       </c>
     </row>
@@ -8443,7 +8668,7 @@
           <t>AVENIDA TORRENCIAL</t>
         </is>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="20">
         <v>3</v>
       </c>
     </row>
@@ -8471,7 +8696,7 @@
           <t>AVENIDA TORRENCIAL</t>
         </is>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="20">
         <v>8</v>
       </c>
     </row>
@@ -8499,7 +8724,7 @@
           <t>AVENIDA TORRENCIAL</t>
         </is>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="20">
         <v>9</v>
       </c>
     </row>
@@ -8527,7 +8752,7 @@
           <t>AVENIDA TORRENCIAL</t>
         </is>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="20">
         <v>3</v>
       </c>
     </row>
@@ -8555,37 +8780,37 @@
           <t>AVENIDA TORRENCIAL</t>
         </is>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="20">
         <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>AVENIDA TORRENCIAL</t>
         </is>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="21">
         <v>32</v>
       </c>
     </row>
@@ -8613,37 +8838,37 @@
           <t>CASO FORTUITO</t>
         </is>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>CASO FORTUITO</t>
         </is>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="21">
         <v>1</v>
       </c>
     </row>
@@ -8671,7 +8896,7 @@
           <t>COLAPSO ESTRUCTURAL</t>
         </is>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="20">
         <v>1</v>
       </c>
     </row>
@@ -8699,37 +8924,37 @@
           <t>COLAPSO ESTRUCTURAL</t>
         </is>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>COLAPSO ESTRUCTURAL</t>
         </is>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="21">
         <v>2</v>
       </c>
     </row>
@@ -8757,7 +8982,7 @@
           <t>CRECIENTE SUBITA</t>
         </is>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="20">
         <v>1</v>
       </c>
     </row>
@@ -8785,7 +9010,7 @@
           <t>CRECIENTE SUBITA</t>
         </is>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="20">
         <v>22</v>
       </c>
     </row>
@@ -8813,37 +9038,37 @@
           <t>CRECIENTE SUBITA</t>
         </is>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="20">
         <v>8</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>CRECIENTE SUBITA</t>
         </is>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="21">
         <v>31</v>
       </c>
     </row>
@@ -8871,7 +9096,7 @@
           <t>EROSION</t>
         </is>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="20">
         <v>1</v>
       </c>
     </row>
@@ -8899,37 +9124,37 @@
           <t>EROSION</t>
         </is>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>EROSION</t>
         </is>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="21">
         <v>2</v>
       </c>
     </row>
@@ -8957,37 +9182,37 @@
           <t>INCENDIO</t>
         </is>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
         <is>
           <t>INCENDIO</t>
         </is>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="21">
         <v>1</v>
       </c>
     </row>
@@ -9015,7 +9240,7 @@
           <t>INCENDIO DE COBERTURA VEGETAL</t>
         </is>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="20">
         <v>3</v>
       </c>
     </row>
@@ -9043,7 +9268,7 @@
           <t>INCENDIO DE COBERTURA VEGETAL</t>
         </is>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="20">
         <v>1</v>
       </c>
     </row>
@@ -9071,37 +9296,37 @@
           <t>INCENDIO DE COBERTURA VEGETAL</t>
         </is>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>INCENDIO DE COBERTURA VEGETAL</t>
         </is>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="21">
         <v>6</v>
       </c>
     </row>
@@ -9129,7 +9354,7 @@
           <t>INCENDIO ESTRUCTURAL</t>
         </is>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="20">
         <v>1</v>
       </c>
     </row>
@@ -9157,7 +9382,7 @@
           <t>INCENDIO ESTRUCTURAL</t>
         </is>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="20">
         <v>2</v>
       </c>
     </row>
@@ -9185,37 +9410,37 @@
           <t>INCENDIO ESTRUCTURAL</t>
         </is>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
         <is>
           <t>INCENDIO ESTRUCTURAL</t>
         </is>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="21">
         <v>4</v>
       </c>
     </row>
@@ -9243,7 +9468,7 @@
           <t>INCENDIO FORESTAL</t>
         </is>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="20">
         <v>9</v>
       </c>
     </row>
@@ -9271,7 +9496,7 @@
           <t>INCENDIO FORESTAL</t>
         </is>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="20">
         <v>4</v>
       </c>
     </row>
@@ -9299,7 +9524,7 @@
           <t>INCENDIO FORESTAL</t>
         </is>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="20">
         <v>4</v>
       </c>
     </row>
@@ -9327,37 +9552,37 @@
           <t>INCENDIO FORESTAL</t>
         </is>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
         <is>
           <t>INCENDIO FORESTAL</t>
         </is>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="21">
         <v>19</v>
       </c>
     </row>
@@ -9385,7 +9610,7 @@
           <t>INUNDACION</t>
         </is>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="20">
         <v>1</v>
       </c>
     </row>
@@ -9413,7 +9638,7 @@
           <t>INUNDACION</t>
         </is>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="20">
         <v>1</v>
       </c>
     </row>
@@ -9441,7 +9666,7 @@
           <t>INUNDACION</t>
         </is>
       </c>
-      <c r="F40" s="14">
+      <c r="F40" s="20">
         <v>3</v>
       </c>
     </row>
@@ -9469,37 +9694,37 @@
           <t>INUNDACION</t>
         </is>
       </c>
-      <c r="F41" s="14">
+      <c r="F41" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
         <is>
           <t>INUNDACION</t>
         </is>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="21">
         <v>6</v>
       </c>
     </row>
@@ -9527,7 +9752,7 @@
           <t>MOVIMIENTO EN MASA</t>
         </is>
       </c>
-      <c r="F43" s="14">
+      <c r="F43" s="20">
         <v>1</v>
       </c>
     </row>
@@ -9555,7 +9780,7 @@
           <t>MOVIMIENTO EN MASA</t>
         </is>
       </c>
-      <c r="F44" s="14">
+      <c r="F44" s="20">
         <v>7</v>
       </c>
     </row>
@@ -9583,7 +9808,7 @@
           <t>MOVIMIENTO EN MASA</t>
         </is>
       </c>
-      <c r="F45" s="14">
+      <c r="F45" s="20">
         <v>15</v>
       </c>
     </row>
@@ -9611,7 +9836,7 @@
           <t>MOVIMIENTO EN MASA</t>
         </is>
       </c>
-      <c r="F46" s="14">
+      <c r="F46" s="20">
         <v>8</v>
       </c>
     </row>
@@ -9639,7 +9864,7 @@
           <t>MOVIMIENTO EN MASA</t>
         </is>
       </c>
-      <c r="F47" s="14">
+      <c r="F47" s="20">
         <v>4</v>
       </c>
     </row>
@@ -9667,37 +9892,37 @@
           <t>MOVIMIENTO EN MASA</t>
         </is>
       </c>
-      <c r="F48" s="14">
+      <c r="F48" s="20">
         <v>9</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
         <is>
           <t>MOVIMIENTO EN MASA</t>
         </is>
       </c>
-      <c r="F49" s="15">
+      <c r="F49" s="21">
         <v>44</v>
       </c>
     </row>
@@ -9725,37 +9950,37 @@
           <t>SISMO</t>
         </is>
       </c>
-      <c r="F50" s="14">
+      <c r="F50" s="20">
         <v>3</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
         <is>
           <t>SISMO</t>
         </is>
       </c>
-      <c r="F51" s="15">
+      <c r="F51" s="21">
         <v>3</v>
       </c>
     </row>
@@ -9783,7 +10008,7 @@
           <t>TEMPORAL</t>
         </is>
       </c>
-      <c r="F52" s="14">
+      <c r="F52" s="20">
         <v>1</v>
       </c>
     </row>
@@ -9811,7 +10036,7 @@
           <t>TEMPORAL</t>
         </is>
       </c>
-      <c r="F53" s="14">
+      <c r="F53" s="20">
         <v>1</v>
       </c>
     </row>
@@ -9839,7 +10064,7 @@
           <t>TEMPORAL</t>
         </is>
       </c>
-      <c r="F54" s="14">
+      <c r="F54" s="20">
         <v>2</v>
       </c>
     </row>
@@ -9867,37 +10092,37 @@
           <t>TEMPORAL</t>
         </is>
       </c>
-      <c r="F55" s="14">
+      <c r="F55" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
         <is>
           <t>TEMPORAL</t>
         </is>
       </c>
-      <c r="F56" s="15">
+      <c r="F56" s="21">
         <v>6</v>
       </c>
     </row>
@@ -9925,7 +10150,7 @@
           <t>TORMENTA ELECTRICA</t>
         </is>
       </c>
-      <c r="F57" s="14">
+      <c r="F57" s="20">
         <v>1</v>
       </c>
     </row>
@@ -9953,37 +10178,37 @@
           <t>TORMENTA ELECTRICA</t>
         </is>
       </c>
-      <c r="F58" s="14">
+      <c r="F58" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E59" s="19" t="inlineStr">
         <is>
           <t>TORMENTA ELECTRICA</t>
         </is>
       </c>
-      <c r="F59" s="15">
+      <c r="F59" s="21">
         <v>2</v>
       </c>
     </row>
@@ -10011,7 +10236,7 @@
           <t>VENDAVAL</t>
         </is>
       </c>
-      <c r="F60" s="14">
+      <c r="F60" s="20">
         <v>6</v>
       </c>
     </row>
@@ -10039,7 +10264,7 @@
           <t>VENDAVAL</t>
         </is>
       </c>
-      <c r="F61" s="14">
+      <c r="F61" s="20">
         <v>3</v>
       </c>
     </row>
@@ -10067,7 +10292,7 @@
           <t>VENDAVAL</t>
         </is>
       </c>
-      <c r="F62" s="14">
+      <c r="F62" s="20">
         <v>3</v>
       </c>
     </row>
@@ -10095,37 +10320,37 @@
           <t>VENDAVAL</t>
         </is>
       </c>
-      <c r="F63" s="14">
+      <c r="F63" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="C64" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr">
         <is>
           <t>VENDAVAL</t>
         </is>
       </c>
-      <c r="F64" s="15">
+      <c r="F64" s="21">
         <v>13</v>
       </c>
     </row>
@@ -10141,41 +10366,41 @@
   <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="23" t="inlineStr">
         <is>
           <t>Número de eventos</t>
         </is>
@@ -10203,7 +10428,7 @@
       <c r="E2">
         <v>2019</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="25">
         <v>1</v>
       </c>
     </row>
@@ -10229,35 +10454,35 @@
       <c r="E3">
         <v>2019</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="25">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E4" s="3">
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E4" s="24">
         <v>2019</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="26">
         <v>3</v>
       </c>
     </row>
@@ -10283,7 +10508,7 @@
       <c r="E5">
         <v>2020</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="25">
         <v>1</v>
       </c>
     </row>
@@ -10309,7 +10534,7 @@
       <c r="E6">
         <v>2020</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="25">
         <v>6</v>
       </c>
     </row>
@@ -10335,7 +10560,7 @@
       <c r="E7">
         <v>2020</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="25">
         <v>5</v>
       </c>
     </row>
@@ -10361,7 +10586,7 @@
       <c r="E8">
         <v>2020</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="25">
         <v>1</v>
       </c>
     </row>
@@ -10387,35 +10612,35 @@
       <c r="E9">
         <v>2020</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="25">
         <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E10" s="3">
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="24">
         <v>2020</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="26">
         <v>22</v>
       </c>
     </row>
@@ -10441,7 +10666,7 @@
       <c r="E11">
         <v>2021</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="25">
         <v>1</v>
       </c>
     </row>
@@ -10467,7 +10692,7 @@
       <c r="E12">
         <v>2021</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="25">
         <v>5</v>
       </c>
     </row>
@@ -10493,7 +10718,7 @@
       <c r="E13">
         <v>2021</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="25">
         <v>8</v>
       </c>
     </row>
@@ -10519,7 +10744,7 @@
       <c r="E14">
         <v>2021</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="25">
         <v>2</v>
       </c>
     </row>
@@ -10545,7 +10770,7 @@
       <c r="E15">
         <v>2021</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="25">
         <v>1</v>
       </c>
     </row>
@@ -10571,35 +10796,35 @@
       <c r="E16">
         <v>2021</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="25">
         <v>7</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E17" s="3">
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E17" s="24">
         <v>2021</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="26">
         <v>24</v>
       </c>
     </row>
@@ -10625,7 +10850,7 @@
       <c r="E18">
         <v>2022</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="25">
         <v>3</v>
       </c>
     </row>
@@ -10651,7 +10876,7 @@
       <c r="E19">
         <v>2022</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="25">
         <v>9</v>
       </c>
     </row>
@@ -10677,7 +10902,7 @@
       <c r="E20">
         <v>2022</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="25">
         <v>33</v>
       </c>
     </row>
@@ -10703,7 +10928,7 @@
       <c r="E21">
         <v>2022</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="25">
         <v>6</v>
       </c>
     </row>
@@ -10729,7 +10954,7 @@
       <c r="E22">
         <v>2022</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="25">
         <v>9</v>
       </c>
     </row>
@@ -10755,35 +10980,35 @@
       <c r="E23">
         <v>2022</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="25">
         <v>18</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E24" s="3">
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E24" s="24">
         <v>2022</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="26">
         <v>78</v>
       </c>
     </row>
@@ -10809,7 +11034,7 @@
       <c r="E25">
         <v>2023</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="25">
         <v>1</v>
       </c>
     </row>
@@ -10835,7 +11060,7 @@
       <c r="E26">
         <v>2023</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="25">
         <v>1</v>
       </c>
     </row>
@@ -10861,7 +11086,7 @@
       <c r="E27">
         <v>2023</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="25">
         <v>11</v>
       </c>
     </row>
@@ -10887,7 +11112,7 @@
       <c r="E28">
         <v>2023</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="25">
         <v>4</v>
       </c>
     </row>
@@ -10913,35 +11138,35 @@
       <c r="E29">
         <v>2023</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="25">
         <v>3</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E30" s="3">
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E30" s="24">
         <v>2023</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="26">
         <v>20</v>
       </c>
     </row>
@@ -10967,7 +11192,7 @@
       <c r="E31">
         <v>2024</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="25">
         <v>1</v>
       </c>
     </row>
@@ -10993,7 +11218,7 @@
       <c r="E32">
         <v>2024</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="25">
         <v>3</v>
       </c>
     </row>
@@ -11019,7 +11244,7 @@
       <c r="E33">
         <v>2024</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="25">
         <v>13</v>
       </c>
     </row>
@@ -11045,7 +11270,7 @@
       <c r="E34">
         <v>2024</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="25">
         <v>6</v>
       </c>
     </row>
@@ -11071,7 +11296,7 @@
       <c r="E35">
         <v>2024</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="25">
         <v>4</v>
       </c>
     </row>
@@ -11097,35 +11322,35 @@
       <c r="E36">
         <v>2024</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="25">
         <v>2</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E37" s="3">
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E37" s="24">
         <v>2024</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="26">
         <v>29</v>
       </c>
     </row>
@@ -11141,64 +11366,64 @@
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="5" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="28" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="28" t="inlineStr">
         <is>
           <t>Avenida torrencial</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="28" t="inlineStr">
         <is>
           <t>Movimiento en masa</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="28" t="inlineStr">
         <is>
           <t>Incendio de cobertura vegetal</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="28" t="inlineStr">
         <is>
           <t>Inundación</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="28" t="inlineStr">
         <is>
           <t>Sequía</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="28" t="inlineStr">
         <is>
           <t>Sismo</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="28" t="inlineStr">
         <is>
           <t>Emergencia más prevalente</t>
         </is>
@@ -11218,22 +11443,22 @@
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="30">
         <v>3</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="32">
         <v>1</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <v>0</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="36">
         <v>0</v>
       </c>
-      <c r="H2" s="26">
+      <c r="H2" s="38">
         <v>0</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="40">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -11256,22 +11481,22 @@
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="30">
         <v>8</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="32">
         <v>7</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <v>0</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="36">
         <v>0</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="38">
         <v>0</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="40">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -11294,22 +11519,22 @@
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="30">
         <v>9</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="32">
         <v>15</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <v>0</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="36">
         <v>1</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="38">
         <v>0</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="40">
         <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -11332,22 +11557,22 @@
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="30">
         <v>0</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="32">
         <v>8</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="34">
         <v>3</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="36">
         <v>1</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="38">
         <v>0</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="40">
         <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -11370,22 +11595,22 @@
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="30">
         <v>3</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="32">
         <v>4</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="34">
         <v>1</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="36">
         <v>3</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="38">
         <v>0</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="40">
         <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -11408,22 +11633,22 @@
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="30">
         <v>9</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="32">
         <v>9</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="34">
         <v>2</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="36">
         <v>1</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="38">
         <v>0</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="40">
         <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -11433,80 +11658,80 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="19">
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="31">
         <v>32</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <v>44</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="35">
         <v>6</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="37">
         <v>6</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="39">
         <v>0</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="41">
         <v>3</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="29" t="inlineStr">
         <is>
           <t>Movimiento en masa</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN OCCIDENTE</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="19">
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D9" s="31">
         <v>52</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <v>203</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="35">
         <v>33</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="37">
         <v>19</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="39">
         <v>0</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="41">
         <v>3</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="29" t="inlineStr">
         <is>
           <t>Movimiento en masa</t>
         </is>
@@ -11524,41 +11749,41 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="55.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="43" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="43" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="43" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="43" t="inlineStr">
         <is>
           <t>IMRC Exceso de lluvias</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="43" t="inlineStr">
         <is>
           <t>IMRC Déficit de lluvias</t>
         </is>
@@ -11583,10 +11808,10 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="30">
+      <c r="E2" s="45">
         <v>56.6213869105825</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="47">
         <v>24.29138941191</v>
       </c>
     </row>
@@ -11609,10 +11834,10 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="45">
         <v>61.804414394444</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="47">
         <v>24.6856653008425</v>
       </c>
     </row>
@@ -11635,10 +11860,10 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="45">
         <v>68.6185410581765</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="47">
         <v>27.5670020996842</v>
       </c>
     </row>
@@ -11661,10 +11886,10 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="45">
         <v>57.2075313164373</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="47">
         <v>21.3267721402843</v>
       </c>
     </row>
@@ -11687,10 +11912,10 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="45">
         <v>61.5185215873653</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="47">
         <v>35.0933177896083</v>
       </c>
     </row>
@@ -11713,66 +11938,66 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="45">
         <v>59.44018053976</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="47">
         <v>31.2703781762203</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="44" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="E8" s="31">
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="E8" s="46">
         <v>60.8684293011276</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="48">
         <v>27.3724208197583</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="46">
         <v>46.9223181824352</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="48">
         <v>26.5093698141241</v>
       </c>
     </row>
@@ -11788,35 +12013,35 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="55.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="50" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="50" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="50" t="inlineStr">
         <is>
           <t>Pérdida de cobertura arbórea 2001-2023 (%)</t>
         </is>
@@ -11841,7 +12066,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="34">
+      <c r="E2" s="52">
         <v>0.04</v>
       </c>
     </row>
@@ -11864,7 +12089,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="52">
         <v>0.055</v>
       </c>
     </row>
@@ -11887,7 +12112,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="34">
+      <c r="E4" s="52">
         <v>0.037</v>
       </c>
     </row>
@@ -11910,7 +12135,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="52">
         <v>0.032</v>
       </c>
     </row>
@@ -11933,7 +12158,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="52">
         <v>0.034</v>
       </c>
     </row>
@@ -11956,82 +12181,82 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="52">
         <v>0.074</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="51" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="35">
+      <c r="C8" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="53">
         <v>0.0453333333333333</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" s="51" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE SUBREGIÓN OCCIDENTE</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="35">
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E9" s="53">
         <v>0.0422631578947368</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="51" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E10" s="35">
+      <c r="C10" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="53">
         <v>0.09304</v>
       </c>
     </row>
@@ -12047,23 +12272,23 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="55" t="inlineStr">
         <is>
           <t>area_km2</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="55" t="inlineStr">
         <is>
           <t>participacion</t>
         </is>
@@ -12146,29 +12371,29 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>irca</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>irca_urbano</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="57" t="inlineStr">
         <is>
           <t>irca_rural</t>
         </is>
